--- a/queso.xlsx
+++ b/queso.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Justie\Desktop\Tareas\Programacion para Ingenieros\Segundo parcial\Python-Grading-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A82F895-7BA9-4815-8D22-4EEFF8400D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDCB640-B741-4FD1-A877-56D4E716C7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{31155351-1F80-42E9-8E3F-3E72490812C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{31155351-1F80-42E9-8E3F-3E72490812C9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="promedio" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,6 +33,32 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>MATRICULA</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>APELLIDO</t>
+  </si>
+  <si>
+    <t>1P</t>
+  </si>
+  <si>
+    <t>2P</t>
+  </si>
+  <si>
+    <t>3P</t>
+  </si>
+  <si>
+    <t>PROMEDIO</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +428,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613C4F1A-D62C-42EF-BB3A-97E75762D94A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,89 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">Matricula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right to exam</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -91,53 +58,110 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -314,78 +338,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="8.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="9.14"/>
+    <col width="10.86" customWidth="1" style="3" min="1" max="1"/>
+    <col width="8.710000000000001" customWidth="1" style="3" min="2" max="2"/>
+    <col width="8.31" customWidth="1" style="3" min="3" max="5"/>
+    <col width="10.57" customWidth="1" style="3" min="6" max="6"/>
+    <col width="17.02" customWidth="1" style="3" min="7" max="7"/>
+    <col width="9.140000000000001" customWidth="1" style="3" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
+    <row r="1" ht="15" customHeight="1" s="4">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Matricula</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Parcial 1</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Parcial 2</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Parcial 3</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Right to exam</t>
+        </is>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+    <row r="2" ht="15" customHeight="1" s="4">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>has right</t>
+        </is>
+      </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+    <row r="3" ht="15" customHeight="1" s="4">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>has right</t>
+        </is>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+    <row r="4" ht="15" customHeight="1" s="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>has right</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,89 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">Matricula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right to exam</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -91,53 +58,110 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -314,78 +338,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="8.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="9.14"/>
+    <col width="10.86" customWidth="1" style="3" min="1" max="1"/>
+    <col width="8.710000000000001" customWidth="1" style="3" min="2" max="2"/>
+    <col width="8.31" customWidth="1" style="3" min="3" max="5"/>
+    <col width="10.57" customWidth="1" style="3" min="6" max="6"/>
+    <col width="17.02" customWidth="1" style="3" min="7" max="7"/>
+    <col width="9.140000000000001" customWidth="1" style="3" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+    <row r="1" ht="15" customHeight="1" s="4">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Matricula</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Parcial 1</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Parcial 2</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Parcial 3</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Right to exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="4">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="4">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+    <row r="4" ht="15" customHeight="1" s="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,70 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/471dfabb4741d0d0/Desktop/PROGR^J ESCU/python/Python-Grading-System/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D8F10C661210B7E50121B7B73FA1A2D1946B6A28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E36ACE-C5A7-4D28-9C26-2F072A6EA113}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" r:id="rId1"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Matricula</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Parcial 1</t>
-  </si>
-  <si>
-    <t>Parcial 2</t>
-  </si>
-  <si>
-    <t>Parcial 3</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Right to exam</t>
-  </si>
-  <si>
-    <t>394468</t>
-  </si>
-  <si>
-    <t>Josue Caleb Escobedo Herrera</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -83,27 +46,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -282,77 +304,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.33203125" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="16384" max="16384" width="9.109375" customWidth="1"/>
+    <col width="10.88671875" customWidth="1" min="1" max="1"/>
+    <col width="25.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.33203125" customWidth="1" min="3" max="5"/>
+    <col width="10.5546875" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="9.109375" customWidth="1" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Matricula</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Right to exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>394569</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Eric Gallo Gardea</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="D2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>394468</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Josue Caleb Escobedo Herrera</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
     </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,33 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dante\source\repos\Python-Grading-System\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B79506C-D6D2-418F-8102-9C90A16EA986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="promedio" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Matricula</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Parcial 1</t>
+  </si>
+  <si>
+    <t>Parcial 2</t>
+  </si>
+  <si>
+    <t>Parcial 3</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Right to exam</t>
+  </si>
+  <si>
+    <t>394569</t>
+  </si>
+  <si>
+    <t>Eric Gallo Gardea</t>
+  </si>
+  <si>
+    <t>394468</t>
+  </si>
+  <si>
+    <t>Josue Caleb Escobedo Herrera</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,86 +89,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -304,113 +288,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10.88671875" customWidth="1" min="1" max="1"/>
-    <col width="25.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.33203125" customWidth="1" min="3" max="5"/>
-    <col width="10.5546875" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="9.109375" customWidth="1" min="16384" max="16384"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="16384" max="16384" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Matricula</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Right to exam</t>
-        </is>
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>394569</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Eric Gallo Gardea</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>394468</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Josue Caleb Escobedo Herrera</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,76 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dante\source\repos\Python-Grading-System\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B79506C-D6D2-418F-8102-9C90A16EA986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" r:id="rId1"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Matricula</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Parcial 1</t>
-  </si>
-  <si>
-    <t>Parcial 2</t>
-  </si>
-  <si>
-    <t>Parcial 3</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Right to exam</t>
-  </si>
-  <si>
-    <t>394569</t>
-  </si>
-  <si>
-    <t>Eric Gallo Gardea</t>
-  </si>
-  <si>
-    <t>394468</t>
-  </si>
-  <si>
-    <t>Josue Caleb Escobedo Herrera</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,27 +46,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -288,78 +304,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="16384" max="16384" width="9.140625" customWidth="1"/>
+    <col width="10.85546875" customWidth="1" min="1" max="1"/>
+    <col width="25.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.28515625" customWidth="1" min="3" max="5"/>
+    <col width="10.5703125" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="9.140625" customWidth="1" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Matricula</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Right to exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>394569</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Eric Gallo Gardea</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="D2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>394468</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Josue Caleb Escobedo Herrera</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
     </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>526228</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,40 +1,105 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t xml:space="preserve">Matricula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right to exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">394569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric Gallo Gardea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">394468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josue Caleb Escobedo Herrera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justie Loya</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+  </numFmts>
+  <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -42,95 +107,62 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -172,12 +204,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -209,7 +241,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -233,7 +265,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -293,80 +325,59 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="10.85546875" customWidth="1" min="1" max="1"/>
-    <col width="25.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.28515625" customWidth="1" min="3" max="5"/>
-    <col width="10.5703125" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="9.140625" customWidth="1" min="16384" max="16384"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Matricula</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Right to exam</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>394569</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Eric Gallo Gardea</t>
-        </is>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>6</v>
@@ -377,19 +388,15 @@
       <c r="E2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>394468</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Josue Caleb Escobedo Herrera</t>
-        </is>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>8</v>
@@ -400,23 +407,53 @@
       <c r="E3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>526228</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
+        <v>394350</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="promedio" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="credits" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t xml:space="preserve">Matricula</t>
   </si>
@@ -56,6 +57,15 @@
   </si>
   <si>
     <t xml:space="preserve">Justie Loya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric Galo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josue Caleb</t>
   </si>
 </sst>
 </file>
@@ -456,4 +466,46 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.84"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -59,13 +59,13 @@
     <t xml:space="preserve">Justie Loya</t>
   </si>
   <si>
-    <t xml:space="preserve">Nombres</t>
+    <t xml:space="preserve">Desarrolladores</t>
   </si>
   <si>
     <t xml:space="preserve">Eric Galo</t>
   </si>
   <si>
-    <t xml:space="preserve">Josue Caleb</t>
+    <t xml:space="preserve">Josue Escobedo</t>
   </si>
 </sst>
 </file>
@@ -142,20 +142,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -351,111 +355,111 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>394350</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -476,26 +480,26 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
     </row>

--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,103 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dante\source\repos\Python-Grading-System\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AFC77B-0B92-4E16-8163-E33113957FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="credits" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="promedio" sheetId="1" r:id="rId1"/>
+    <sheet name="credits" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
-    <t xml:space="preserve">Matricula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right to exam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">394569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric Gallo Gardea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">394468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josue Caleb Escobedo Herrera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justie Loya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric Galo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josue Caleb</t>
+    <t>Matricula</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Parcial 1</t>
+  </si>
+  <si>
+    <t>Parcial 2</t>
+  </si>
+  <si>
+    <t>Parcial 3</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Right to exam</t>
+  </si>
+  <si>
+    <t>394569</t>
+  </si>
+  <si>
+    <t>Eric Gallo Gardea</t>
+  </si>
+  <si>
+    <t>394468</t>
+  </si>
+  <si>
+    <t>Josue Caleb Escobedo Herrera</t>
+  </si>
+  <si>
+    <t>Justie Loya</t>
+  </si>
+  <si>
+    <t>Nombres</t>
+  </si>
+  <si>
+    <t>Eric Galo</t>
+  </si>
+  <si>
+    <t>Josue Caleb</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,7 +90,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -117,62 +98,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -214,12 +169,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -251,7 +206,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -275,7 +230,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -335,31 +290,30 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="9.14"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="5" width="8.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="16384" max="16384" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,130 +336,121 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>6</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2">
         <v>8</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>394350</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="1">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="1">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="1">
         <v>10</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.84"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,89 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dante\source\repos\Python-Grading-System\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AFC77B-0B92-4E16-8163-E33113957FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1380" yWindow="0" windowWidth="23805" windowHeight="15750" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" r:id="rId1"/>
-    <sheet name="credits" sheetId="2" r:id="rId2"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="credits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>Matricula</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Parcial 1</t>
-  </si>
-  <si>
-    <t>Parcial 2</t>
-  </si>
-  <si>
-    <t>Parcial 3</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Right to exam</t>
-  </si>
-  <si>
-    <t>394569</t>
-  </si>
-  <si>
-    <t>Eric Gallo Gardea</t>
-  </si>
-  <si>
-    <t>394468</t>
-  </si>
-  <si>
-    <t>Josue Caleb Escobedo Herrera</t>
-  </si>
-  <si>
-    <t>Justie Loya</t>
-  </si>
-  <si>
-    <t>Nombres</t>
-  </si>
-  <si>
-    <t>Eric Galo</t>
-  </si>
-  <si>
-    <t>Josue Caleb</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -101,28 +46,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -301,115 +302,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" customWidth="1"/>
-    <col min="3" max="5" width="8.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="16384" max="16384" width="9.140625" customWidth="1"/>
+    <col width="10.85546875" customWidth="1" min="1" max="1"/>
+    <col width="25.85546875" customWidth="1" min="2" max="2"/>
+    <col width="8.28515625" customWidth="1" min="3" max="5"/>
+    <col width="10.5703125" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="9.140625" customWidth="1" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Matricula</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Parcial 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Right to exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="1" t="n">
+        <v>394350</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Justie Loya</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>394350</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="D2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="1">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>394468</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Josue Caleb Escobedo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>394569</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -418,39 +407,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col width="10.85546875" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
+    <row r="1" ht="12.75" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nombres</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eric Galo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Josue Caleb</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Justie Loya</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,34 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/471dfabb4741d0d0/Desktop/PROGR^J ESCU/python/Python-Grading-System/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_EEC1E55946942AFEF87321B99FB04107B45490B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C780900D-2DD3-47BC-B97D-2E744603806C}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1380" yWindow="0" windowWidth="23805" windowHeight="15750" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="credits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="promedio" sheetId="1" r:id="rId1"/>
+    <sheet name="credits" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Right to exam</t>
+  </si>
+  <si>
+    <t>Justie Loya</t>
+  </si>
+  <si>
+    <t>394468</t>
+  </si>
+  <si>
+    <t>Josue Caleb Escobedo Herrera</t>
+  </si>
+  <si>
+    <t>394569</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>Nombres</t>
+  </si>
+  <si>
+    <t>Eric Galo</t>
+  </si>
+  <si>
+    <t>Josue Caleb</t>
+  </si>
+  <si>
+    <t>Partial 1</t>
+  </si>
+  <si>
+    <t>Partial 2</t>
+  </si>
+  <si>
+    <t>Partial 3</t>
+  </si>
+  <si>
+    <t>Aprobed</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,83 +105,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -302,102 +301,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10.85546875" customWidth="1" min="1" max="1"/>
-    <col width="25.85546875" customWidth="1" min="2" max="2"/>
-    <col width="8.28515625" customWidth="1" min="3" max="5"/>
-    <col width="10.5703125" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="9.140625" customWidth="1" min="16384" max="16384"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Matricula</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Parcial 3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Right to exam</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>394350</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Justie Loya</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="1">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="1">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>394468</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Josue Caleb Escobedo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>394569</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eric</t>
-        </is>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -407,55 +382,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10.85546875" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nombres</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eric Galo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Josue Caleb</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Justie Loya</t>
-        </is>
+    <row r="1" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/queso.xlsx
+++ b/queso.xlsx
@@ -1,87 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/471dfabb4741d0d0/Desktop/PROGR^J ESCU/python/Python-Grading-System/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_EEC1E55946942AFEF87321B99FB04107B45490B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C780900D-2DD3-47BC-B97D-2E744603806C}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="promedio" sheetId="1" r:id="rId1"/>
-    <sheet name="credits" sheetId="2" r:id="rId2"/>
+    <sheet name="promedio" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="credits" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Right to exam</t>
-  </si>
-  <si>
-    <t>Justie Loya</t>
-  </si>
-  <si>
-    <t>394468</t>
-  </si>
-  <si>
-    <t>Josue Caleb Escobedo Herrera</t>
-  </si>
-  <si>
-    <t>394569</t>
-  </si>
-  <si>
-    <t>Eric</t>
-  </si>
-  <si>
-    <t>Nombres</t>
-  </si>
-  <si>
-    <t>Eric Galo</t>
-  </si>
-  <si>
-    <t>Josue Caleb</t>
-  </si>
-  <si>
-    <t>Partial 1</t>
-  </si>
-  <si>
-    <t>Partial 2</t>
-  </si>
-  <si>
-    <t>Partial 3</t>
-  </si>
-  <si>
-    <t>Aprobed</t>
-  </si>
-  <si>
-    <t>ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aproved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right to non-ordinary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justie Loya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">394468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josue Caleb Escobedo Herrera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doesn't have right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">394569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric Galo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josue Caleb</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,7 +117,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -101,33 +125,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -169,12 +218,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -206,7 +255,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -230,7 +279,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -290,129 +339,170 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H1048576"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16384" max="16384" width="9.140625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>394350</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>394350</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1048565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>

--- a/queso.xlsx
+++ b/queso.xlsx
@@ -49,7 +49,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -311,8 +311,10 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col width="10.85546875" customWidth="1" min="1" max="1"/>
-    <col width="25.85546875" customWidth="1" min="2" max="2"/>
-    <col width="8.28515625" customWidth="1" min="3" max="5"/>
+    <col width="28.140625" customWidth="1" min="2" max="2"/>
+    <col width="9.85546875" customWidth="1" min="3" max="3"/>
+    <col width="9.140625" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10.5703125" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="9.140625" customWidth="1" min="16384" max="16384"/>
@@ -377,16 +379,21 @@
       <c r="G2" s="1" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>394468</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Josue Caleb Escobedo Herrera</t>
         </is>
       </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -396,7 +403,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Eric Gallo Gardea</t>
         </is>
       </c>
     </row>
